--- a/etf_holdings/2026-10-27_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,25 +504,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.36%1085</t>
+          <t>-0.79%1255</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1085</v>
+        <v>1255</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.68%1,530,000</t>
+          <t>7.68%1,299,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,11 +531,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1530000</v>
+        <v>1299000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.6%1265</t>
+          <t>-2.3%1060</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1265</v>
+        <v>1060</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.61%1,299,000</t>
+          <t>7.64%1,530,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.64%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1299000</v>
+        <v>1530000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.3%4890</t>
+          <t>-2.04%4790</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4890</v>
+        <v>4790</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.31%323,000</t>
+          <t>7.29%323,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.31%</t>
+          <t>7.29%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-7.12%6070</t>
+          <t>-3.46%5860</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6070</v>
+        <v>5860</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.30%260,000</t>
+          <t>7.18%260,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>7.18%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.19%7585</t>
+          <t>+0.03%16015</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7585</v>
+        <v>16015</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.07%173,000</t>
+          <t>5.98%79,300</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>5.98%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>173000</v>
+        <v>79300</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,34 +809,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.06%16010</t>
+          <t>-3.14%1080</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>16010</v>
+        <v>1080</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.88%79,300</t>
+          <t>5.73%1,127,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>5.73%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>79300</v>
+        <v>1127000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.69%1115</t>
+          <t>-1.25%3960</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1115</v>
+        <v>3960</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.82%1,127,000</t>
+          <t>5.48%294,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.82%</t>
+          <t>5.48%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1127000</v>
+        <v>294000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.85%1875</t>
+          <t>-7.47%1735</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-7.47%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1875</v>
+        <v>1735</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.77%665,000</t>
+          <t>5.44%665,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>5.44%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.14%4010</t>
+          <t>-0.85%1760</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4010</v>
+        <v>1760</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.46%294,000</t>
+          <t>5.05%609,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>294000</v>
+        <v>609000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.2%1775</t>
+          <t>-6.31%4750</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-6.31%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1775</v>
+        <v>4750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.00%609,000</t>
+          <t>4.74%212,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>609000</v>
+        <v>212000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.6%5070</t>
+          <t>+2.39%814</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+2.39%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5070</v>
+        <v>814</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.97%212,000</t>
+          <t>3.95%1,030,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>212000</v>
+        <v>1030000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.78%3145</t>
+          <t>-1.23%5210</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3145</v>
+        <v>5210</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.05%278,000</t>
+          <t>2.95%120,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>278000</v>
+        <v>120000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.33%795</t>
+          <t>-3.64%2250</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.33%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>795</v>
+        <v>2250</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.79%1,030,000</t>
+          <t>2.87%271,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1030000</v>
+        <v>271000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.51%2335</t>
+          <t>-2.04%7430</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2335</v>
+        <v>7430</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.69%341,000</t>
+          <t>2.56%73,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>341000</v>
+        <v>73000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:08</t>
+          <t>2026-10-27 22:42:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.83%5275</t>
+          <t>+0.56%9810</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5275</v>
+        <v>9810</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.93%120,000</t>
+          <t>2.31%50,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.22%9755</t>
+          <t>+0.63%2400</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9755</v>
+        <v>2400</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.26%50,000</t>
+          <t>2.02%179,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>50000</v>
+        <v>179000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-5.33%1420</t>
+          <t>-0.48%3130</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1420</v>
+        <v>3130</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.01%306,000</t>
+          <t>1.89%128,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>306000</v>
+        <v>128000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.45%2385</t>
+          <t>-9.86%1280</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-9.86%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2385</v>
+        <v>1280</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.98%179,000</t>
+          <t>1.85%306,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>179000</v>
+        <v>306000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.02%1560</t>
+          <t>-6.09%1465</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1560</v>
+        <v>1465</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.44%200,000</t>
+          <t>1.38%200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-5.26%1260</t>
+          <t>+5.98%1950</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1260</v>
+        <v>1950</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.86%148,000</t>
+          <t>0.91%99,139</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>148000</v>
+        <v>99139</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.13%1840</t>
+          <t>+1.98%1285</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1840</v>
+        <v>1285</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.84%99,139</t>
+          <t>0.90%148,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>99139</v>
+        <v>148000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4%1560</t>
+          <t>-3.21%1510</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1560</v>
+        <v>1510</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.68%94,000</t>
+          <t>0.67%94,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.47%778</t>
+          <t>-0.42%4775</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.47%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>778</v>
+        <v>4775</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.53%146,000</t>
+          <t>0.52%23,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>146000</v>
+        <v>23000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.52%4795</t>
+          <t>-4.56%941</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-4.56%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4795</v>
+        <v>941</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>0.22%50,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>23000</v>
+        <v>50000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.38%986</t>
+          <t>+0.31%161.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>986</v>
+        <v>161.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.23%50,000</t>
+          <t>0.16%211,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>50000</v>
+        <v>211000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.3%161</t>
+          <t>-0.87%228</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.16%211,000</t>
+          <t>0.11%100,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>211000</v>
+        <v>100000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.69%230</t>
+          <t>+2.48%269</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.11%100,000</t>
+          <t>0.05%42,650</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>100000</v>
+        <v>42650</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.58%262.5</t>
+          <t>+0.61%248</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.58%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>262.5</v>
+        <v>248</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.05%42,650</t>
+          <t>0.04%34,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>42650</v>
+        <v>34000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.98%246.5</t>
+          <t>-2.83%6000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>246.5</v>
+        <v>6000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.04%34,000</t>
+          <t>0.03%1,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>34000</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:09</t>
+          <t>2026-10-27 22:42:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.08%6175</t>
+          <t>-9.6%433</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6175</v>
+        <v>433</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.03%1,000</t>
+          <t>0.02%10,217</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>10217</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-5.34%479</t>
+          <t>0%3495</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.34%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>479</v>
+        <v>3495</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.02%10,217</t>
+          <t>0.02%1,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>10217</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.95%125.5</t>
+          <t>-2.39%122.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>125.5</v>
+        <v>122.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.8%3495</t>
+          <t>+2.54%687</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3495</v>
+        <v>687</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>0.02%5,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.9%670</t>
+          <t>-5.06%2910</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-5.06%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>670</v>
+        <v>2910</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.02%5,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-5.11%3065</t>
+          <t>-4.13%278.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.11%</t>
+          <t>-4.13%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3065</v>
+        <v>278.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.01%10,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-8.21%290.5</t>
+          <t>+2.59%1190</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>+2.59%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>290.5</v>
+        <v>1190</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.01%10,000</t>
+          <t>0.01%2,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.28%1160</t>
+          <t>+1.18%429</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1160</v>
+        <v>429</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.01%2,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-5.78%424</t>
+          <t>-0.46%651</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.78%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>424</v>
+        <v>651</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>&lt;0.01%5,000</t>
+          <t>&lt;0.01%3,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.39%654</t>
+          <t>+7.24%1925</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+7.24%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>654</v>
+        <v>1925</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%3,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>3605宏致</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.37%1795</t>
+          <t>-9.04%156</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-9.04%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1795</v>
+        <v>156</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%10,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3605宏致</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.65%171.5</t>
+          <t>-1.16%297.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>171.5</v>
+        <v>297.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%10,000</t>
+          <t>&lt;0.01%5,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-6.08%301</t>
+          <t>-3.41%1275</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>-3.41%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>301</v>
+        <v>1275</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>&lt;0.01%5,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-7.69%1320</t>
+          <t>+3.64%1140</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>+3.64%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1320</v>
+        <v>1140</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.79%1100</t>
+          <t>+1.15%97</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>+1.15%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1100</v>
+        <v>97</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%10,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 00:08:10</t>
+          <t>2026-10-27 22:42:51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-6.44%95.9</t>
+          <t>-4.63%742</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.44%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>95.90000000000001</v>
+        <v>742</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>&lt;0.01%10,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-27_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:48</t>
+          <t>2026-10-27 22:55:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:50</t>
+          <t>2026-10-27 22:55:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:42:51</t>
+          <t>2026-10-27 22:55:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-27_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:19</t>
+          <t>2026-10-27 23:23:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:22</t>
+          <t>2026-10-27 23:23:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:23</t>
+          <t>2026-10-27 23:23:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
